--- a/AUDIO-PROD-01_Reporte_Produccion_Carlos_2026-09-12.xlsx
+++ b/AUDIO-PROD-01_Reporte_Produccion_Carlos_2026-09-12.xlsx
@@ -659,17 +659,17 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -732,17 +732,17 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -805,17 +805,17 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -878,17 +878,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -1024,17 +1024,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1097,17 +1097,17 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1243,17 +1243,17 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1389,17 +1389,17 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1462,17 +1462,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1535,17 +1535,17 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1608,17 +1608,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1754,17 +1754,17 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1827,17 +1827,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1900,17 +1900,17 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1973,17 +1973,17 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2192,17 +2192,17 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2265,17 +2265,17 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -2338,17 +2338,17 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -2411,17 +2411,17 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -2484,17 +2484,17 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2630,17 +2630,17 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2703,17 +2703,17 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2776,17 +2776,17 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2849,17 +2849,17 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Escritorio: Linux · Móvil: emulación Chromium 390×844</t>
+          <t>Escritorio: Linux · Móvil: teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser), desktop y móvil emulado</t>
+          <t>Escritorio: Chromium (Cursor browser) · Móvil: navegador del teléfono físico</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>PASS (viewport emulado 390×844; ver hoja Entorno)</t>
+          <t>PASS (teléfono físico, 2026-09-15). Complementa la emulación 390×844 del 2026-09-12.</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS — checklist AUDIO-PROD-01 completo, incluida reproducción 31/31 en teléfono físico (evidencia B-08).</t>
         </is>
       </c>
     </row>
@@ -3188,6 +3188,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -3263,7 +3264,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-12 (desktop) / 2026-09-15 (móvil físico)</t>
         </is>
       </c>
     </row>
@@ -3279,6 +3280,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
@@ -3406,6 +3408,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
@@ -3421,7 +3424,7 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Emulación Chromium 390×844 (viewport móvil; no dispositivo físico)</t>
+          <t>Teléfono físico (validación de Carlos, 2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -3433,7 +3436,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Viewport móvil emulado (no se usó teléfono físico en esta pasada)</t>
+          <t>Teléfono físico — no se registró marca/modelo en esta actualización</t>
         </is>
       </c>
     </row>
@@ -3445,7 +3448,7 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Chromium (Cursor browser)</t>
+          <t>Navegador del teléfono físico (validación de Carlos)</t>
         </is>
       </c>
     </row>
@@ -3457,7 +3460,7 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -3479,9 +3482,9 @@
           <t>Controles de audio accesibles</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>PASS (verificados en ficha EMP-009: Play US y Play UK)</t>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>PASS — controles US/UK accesibles en teléfono físico (EMP-009)</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3508,7 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>PASS — 31/31 en teléfono físico (2026-09-15)</t>
         </is>
       </c>
     </row>
@@ -3527,9 +3530,9 @@
           <t>Selección U.S./U.K. en EMP-009</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>PASS — botones US y UK independientes y activos</t>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>PASS — US y UK independientes en teléfono físico (EMP-009)</t>
         </is>
       </c>
     </row>
@@ -3539,9 +3542,9 @@
           <t>Resultado móvil</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>PASS (emulación 390×844). No sustituye la verificación B-10 en dispositivo físico si el Hito B la exige aparte.</t>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>PASS — teléfono físico, 31/31. La emulación 390×844 del 2026-09-12 queda como evidencia complementaria, no como único soporte.</t>
         </is>
       </c>
     </row>
